--- a/tables/datas/__tables__.xlsx
+++ b/tables/datas/__tables__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="15855" windowHeight="8145" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -1187,6 +1187,79 @@
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/tables/datas/__tables__.xlsx
+++ b/tables/datas/__tables__.xlsx
@@ -1177,9 +1177,15 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" s="2" t="n"/>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="2" t="n"/>

--- a/tables/datas/__tables__.xlsx
+++ b/tables/datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -1178,23 +1178,86 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>common.TbStoryChapter</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>StoryChapterBean</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>common/#StoryChapterData-剧情章节表.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>剧情章节</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>common.TbStoryDialogue</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>StoryDialogueBean</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>common/#StoryDialogueData-剧情对话表.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>剧情对话</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
@@ -1248,24 +1311,6 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
     </row>
-    <row r="12">
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
